--- a/Entregables/matriz-entregables-17-09.xlsx
+++ b/Entregables/matriz-entregables-17-09.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://frbautneduar-my.sharepoint.com/personal/jomansilla_frba_utn_edu_ar/Documents/04-Cuarto-Año-2026/Administracion-De-Sistemas-De-Información/TPA/Entregables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{8BA3213A-F9A2-4336-B509-36FA0814BE33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE152545-AD83-4D3C-B5CA-7F753CBF5261}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="8_{8BA3213A-F9A2-4336-B509-36FA0814BE33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB0BB09D-FC1E-4950-A3CF-67C15C9CD606}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="480" windowWidth="38640" windowHeight="21240" xr2:uid="{A0C85513-313E-40CE-9B7D-FF496B2AC70C}"/>
+    <workbookView minimized="1" xWindow="1620" yWindow="2280" windowWidth="26085" windowHeight="15705" xr2:uid="{A0C85513-313E-40CE-9B7D-FF496B2AC70C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="297">
   <si>
     <t>ID</t>
   </si>
@@ -926,14 +926,17 @@
     <t>Drive / PPT</t>
   </si>
   <si>
-    <t>Beca 360 - Matriz de Entregables</t>
+    <t>Matriz de Entregables</t>
+  </si>
+  <si>
+    <t>“Desarrollo e implementación de la plataforma Integral para la Gestión y Administración de Becas Académicas (Beca360)”</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -968,13 +971,19 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Roboto"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Roboto"/>
     </font>
@@ -1005,7 +1014,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1104,32 +1113,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF742932"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF742932"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF742932"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF742932"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF742932"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1144,11 +1127,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF742932"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF742932"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1207,10 +1229,22 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1228,6 +1262,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1547,7 +1585,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC008BB9-7F8C-4751-8A3E-30AE819FF0DB}">
-  <dimension ref="B1:H66"/>
+  <dimension ref="B1:H67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.7109375" customWidth="1"/>
@@ -1562,1491 +1600,1503 @@
   <sheetData>
     <row r="1" spans="2:8" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="19" t="s">
         <v>295</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-    </row>
-    <row r="3" spans="2:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="19" t="s">
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+    </row>
+    <row r="3" spans="2:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="24" t="s">
+        <v>296</v>
+      </c>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+    </row>
+    <row r="4" spans="2:8" ht="24" x14ac:dyDescent="0.25">
+      <c r="B4" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C4" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D4" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F4" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="G4" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="20" t="s">
+      <c r="H4" s="25" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="1" t="s">
+    <row r="5" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C5" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D5" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E5" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F5" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G5" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H5" s="23" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="5" t="s">
+    <row r="6" spans="2:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G6" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H6" s="8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="1" t="s">
+    <row r="7" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H7" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="5" t="s">
+    <row r="8" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E8" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F8" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G8" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H8" s="8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="1" t="s">
+    <row r="9" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H9" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="5" t="s">
+    <row r="10" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C10" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D10" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E10" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F10" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H10" s="8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="1" t="s">
+    <row r="11" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H11" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="5" t="s">
+    <row r="12" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C12" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D12" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E12" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G12" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H12" s="8" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="1" t="s">
+    <row r="13" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G13" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H13" s="4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="5" t="s">
+    <row r="14" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C14" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D14" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E14" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F14" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G14" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="H14" s="8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="1" t="s">
+    <row r="15" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G15" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H15" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="5" t="s">
+    <row r="16" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C16" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D16" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E16" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F16" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G16" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="H16" s="8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="1" t="s">
+    <row r="17" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G17" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H17" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="5" t="s">
+    <row r="18" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C18" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D18" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E18" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F18" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="G18" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="H18" s="8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="1" t="s">
+    <row r="19" spans="2:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="G19" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H19" s="4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="5" t="s">
+    <row r="20" spans="2:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C20" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D20" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E20" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F20" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="G20" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="H20" s="8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="1" t="s">
+    <row r="21" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E21" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F21" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G20" s="10" t="s">
+      <c r="G21" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H21" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="5" t="s">
+    <row r="22" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C22" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D22" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E22" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F22" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="G21" s="7" t="s">
+      <c r="G22" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="H22" s="8" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="1" t="s">
+    <row r="23" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F23" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G22" s="11" t="s">
+      <c r="G23" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="H23" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="5" t="s">
+    <row r="24" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C24" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D24" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E24" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F24" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="G24" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="H24" s="8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="1" t="s">
+    <row r="25" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D25" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E25" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F25" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="G24" s="12" t="s">
+      <c r="G25" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="H24" s="4" t="s">
+      <c r="H25" s="4" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="25" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="5" t="s">
+    <row r="26" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C26" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D26" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E26" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="F26" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="G25" s="13" t="s">
+      <c r="G26" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="H25" s="8" t="s">
+      <c r="H26" s="8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="1" t="s">
+    <row r="27" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C27" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D27" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E27" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F27" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G26" s="10" t="s">
+      <c r="G27" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H26" s="4" t="s">
+      <c r="H27" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="5" t="s">
+    <row r="28" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C28" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D28" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E28" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="F28" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G27" s="14" t="s">
+      <c r="G28" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="H27" s="8" t="s">
+      <c r="H28" s="8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="1" t="s">
+    <row r="29" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C29" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D29" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E29" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="F29" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="G28" s="10" t="s">
+      <c r="G29" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="H29" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="2:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="5" t="s">
+    <row r="30" spans="2:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C30" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D30" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E30" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="F30" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G29" s="7" t="s">
+      <c r="G30" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="H29" s="8" t="s">
+      <c r="H30" s="8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="1" t="s">
+    <row r="31" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C31" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D31" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E31" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F31" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="G30" s="11" t="s">
+      <c r="G31" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H30" s="4" t="s">
+      <c r="H31" s="4" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="31" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="5" t="s">
+    <row r="32" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C32" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D32" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E32" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="F32" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="G31" s="9" t="s">
+      <c r="G32" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="H31" s="8" t="s">
+      <c r="H32" s="8" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="1" t="s">
+    <row r="33" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D33" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E33" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="F33" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="G32" s="11" t="s">
+      <c r="G33" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H32" s="4" t="s">
+      <c r="H33" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="5" t="s">
+    <row r="34" spans="2:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C34" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D34" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E34" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="F33" s="6" t="s">
+      <c r="F34" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="G33" s="7" t="s">
+      <c r="G34" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="H33" s="8" t="s">
+      <c r="H34" s="8" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="34" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="1" t="s">
+    <row r="35" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D35" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="F35" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="G35" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="H34" s="4" t="s">
+      <c r="H35" s="4" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="5" t="s">
+    <row r="36" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C36" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D36" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="E36" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="F35" s="6" t="s">
+      <c r="F36" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="G35" s="7" t="s">
+      <c r="G36" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="H35" s="8" t="s">
+      <c r="H36" s="8" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="1" t="s">
+    <row r="37" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C37" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D37" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E37" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="F37" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="G36" s="3" t="s">
+      <c r="G37" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="H36" s="4" t="s">
+      <c r="H37" s="4" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="37" spans="2:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="5" t="s">
+    <row r="38" spans="2:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C38" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="D38" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E37" s="6" t="s">
+      <c r="E38" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="F37" s="6" t="s">
+      <c r="F38" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="G37" s="7" t="s">
+      <c r="G38" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="H37" s="8" t="s">
+      <c r="H38" s="8" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="38" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="1" t="s">
+    <row r="39" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C39" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D39" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="E39" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="F39" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="G38" s="3" t="s">
+      <c r="G39" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H38" s="4" t="s">
+      <c r="H39" s="4" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="39" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="5" t="s">
+    <row r="40" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C40" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="D40" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="E39" s="6" t="s">
+      <c r="E40" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="F39" s="6" t="s">
+      <c r="F40" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="G39" s="13" t="s">
+      <c r="G40" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="H39" s="8" t="s">
+      <c r="H40" s="8" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="1" t="s">
+    <row r="41" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C41" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D41" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="E41" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="F40" s="2" t="s">
+      <c r="F41" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="G40" s="12" t="s">
+      <c r="G41" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="H40" s="4" t="s">
+      <c r="H41" s="4" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="5" t="s">
+    <row r="42" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C42" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D42" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="E42" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="F41" s="6" t="s">
+      <c r="F42" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="G41" s="13" t="s">
+      <c r="G42" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="H41" s="8" t="s">
+      <c r="H42" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="1" t="s">
+    <row r="43" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C43" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D43" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="E42" s="2" t="s">
+      <c r="E43" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="F42" s="2" t="s">
+      <c r="F43" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="G42" s="12" t="s">
+      <c r="G43" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="H42" s="4" t="s">
+      <c r="H43" s="4" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="43" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="5" t="s">
+    <row r="44" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C44" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="D44" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="E43" s="6" t="s">
+      <c r="E44" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="F43" s="6" t="s">
+      <c r="F44" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G43" s="9" t="s">
+      <c r="G44" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="H43" s="8" t="s">
+      <c r="H44" s="8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="1" t="s">
+    <row r="45" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B45" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C45" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="D45" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="E45" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="F44" s="2" t="s">
+      <c r="F45" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="G44" s="12" t="s">
+      <c r="G45" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="H44" s="4" t="s">
+      <c r="H45" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="5" t="s">
+    <row r="46" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="C46" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="D45" s="6" t="s">
+      <c r="D46" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="E45" s="6" t="s">
+      <c r="E46" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="F45" s="6" t="s">
+      <c r="F46" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="G45" s="9" t="s">
+      <c r="G46" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="H45" s="8" t="s">
+      <c r="H46" s="8" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="1" t="s">
+    <row r="47" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C47" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D47" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="E46" s="2" t="s">
+      <c r="E47" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="F46" s="2" t="s">
+      <c r="F47" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="G46" s="11" t="s">
+      <c r="G47" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H46" s="4" t="s">
+      <c r="H47" s="4" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="47" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="5" t="s">
+    <row r="48" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C48" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="D47" s="6" t="s">
+      <c r="D48" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="E47" s="6" t="s">
+      <c r="E48" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="F47" s="6" t="s">
+      <c r="F48" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="G47" s="9" t="s">
+      <c r="G48" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="H47" s="8" t="s">
+      <c r="H48" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="48" spans="2:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="1" t="s">
+    <row r="49" spans="2:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C49" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="D49" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="E49" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="F48" s="2" t="s">
+      <c r="F49" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="G48" s="11" t="s">
+      <c r="G49" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H48" s="4" t="s">
+      <c r="H49" s="4" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="49" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="5" t="s">
+    <row r="50" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B50" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="C50" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="D49" s="6" t="s">
+      <c r="D50" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="E49" s="6" t="s">
+      <c r="E50" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="F49" s="6" t="s">
+      <c r="F50" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="G49" s="14" t="s">
+      <c r="G50" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="H49" s="8" t="s">
+      <c r="H50" s="8" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="50" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="1" t="s">
+    <row r="51" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B51" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C51" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D51" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="E51" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="F50" s="2" t="s">
+      <c r="F51" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="G50" s="10" t="s">
+      <c r="G51" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H50" s="4" t="s">
+      <c r="H51" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="5" t="s">
+    <row r="52" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="C51" s="6" t="s">
+      <c r="C52" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="D51" s="6" t="s">
+      <c r="D52" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="E51" s="6" t="s">
+      <c r="E52" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="F51" s="6" t="s">
+      <c r="F52" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="G51" s="14" t="s">
+      <c r="G52" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="H51" s="8" t="s">
+      <c r="H52" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="52" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="1" t="s">
+    <row r="53" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C53" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="D53" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="E52" s="2" t="s">
+      <c r="E53" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F52" s="2" t="s">
+      <c r="F53" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G52" s="10" t="s">
+      <c r="G53" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H52" s="4" t="s">
+      <c r="H53" s="4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="53" spans="2:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="5" t="s">
+    <row r="54" spans="2:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B54" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C54" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="D53" s="6" t="s">
+      <c r="D54" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="E53" s="6" t="s">
+      <c r="E54" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="F53" s="6" t="s">
+      <c r="F54" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="G53" s="9" t="s">
+      <c r="G54" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="H53" s="8" t="s">
+      <c r="H54" s="8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="1" t="s">
+    <row r="55" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B55" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C55" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="D55" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="E54" s="2" t="s">
+      <c r="E55" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F54" s="2" t="s">
+      <c r="F55" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="G54" s="12" t="s">
+      <c r="G55" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="H54" s="4" t="s">
+      <c r="H55" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="5" t="s">
+    <row r="56" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B56" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C56" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="D55" s="6" t="s">
+      <c r="D56" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="E55" s="6" t="s">
+      <c r="E56" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="F55" s="6" t="s">
+      <c r="F56" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="G55" s="7" t="s">
+      <c r="G56" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="H55" s="8" t="s">
+      <c r="H56" s="8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="56" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="1" t="s">
+    <row r="57" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B57" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C57" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="D57" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="E57" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="F56" s="2" t="s">
+      <c r="F57" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="G56" s="10" t="s">
+      <c r="G57" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H56" s="4" t="s">
+      <c r="H57" s="4" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="57" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="5" t="s">
+    <row r="58" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="C58" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="D57" s="6" t="s">
+      <c r="D58" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="E57" s="6" t="s">
+      <c r="E58" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="F57" s="6" t="s">
+      <c r="F58" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="G57" s="7" t="s">
+      <c r="G58" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="H57" s="8" t="s">
+      <c r="H58" s="8" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="58" spans="2:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="1" t="s">
+    <row r="59" spans="2:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B59" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C59" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="D59" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="E58" s="2" t="s">
+      <c r="E59" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="F58" s="2" t="s">
+      <c r="F59" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G58" s="11" t="s">
+      <c r="G59" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H58" s="4" t="s">
+      <c r="H59" s="4" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="59" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="5" t="s">
+    <row r="60" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="C59" s="6" t="s">
+      <c r="C60" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="D59" s="6" t="s">
+      <c r="D60" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="E59" s="6" t="s">
+      <c r="E60" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="F59" s="6" t="s">
+      <c r="F60" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="G59" s="7" t="s">
+      <c r="G60" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="H59" s="8" t="s">
+      <c r="H60" s="8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="60" spans="2:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="1" t="s">
+    <row r="61" spans="2:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B61" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C61" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="D61" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="E61" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="F60" s="2" t="s">
+      <c r="F61" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="G60" s="3" t="s">
+      <c r="G61" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H60" s="4" t="s">
+      <c r="H61" s="4" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="61" spans="2:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="5" t="s">
+    <row r="62" spans="2:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B62" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="C61" s="6" t="s">
+      <c r="C62" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="D61" s="6" t="s">
+      <c r="D62" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="E61" s="6" t="s">
+      <c r="E62" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="F61" s="6" t="s">
+      <c r="F62" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="G61" s="14" t="s">
+      <c r="G62" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="H61" s="8" t="s">
+      <c r="H62" s="8" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="62" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="1" t="s">
+    <row r="63" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C63" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="D63" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="E62" s="2" t="s">
+      <c r="E63" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="F62" s="2" t="s">
+      <c r="F63" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G62" s="10" t="s">
+      <c r="G63" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H62" s="4" t="s">
+      <c r="H63" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="5" t="s">
+    <row r="64" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B64" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="C63" s="6" t="s">
+      <c r="C64" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="D63" s="6" t="s">
+      <c r="D64" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="E63" s="6" t="s">
+      <c r="E64" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="F63" s="6" t="s">
+      <c r="F64" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="G63" s="9" t="s">
+      <c r="G64" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="H63" s="8" t="s">
+      <c r="H64" s="8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="1" t="s">
+    <row r="65" spans="2:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B65" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C65" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="D65" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="E64" s="2" t="s">
+      <c r="E65" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="F64" s="2" t="s">
+      <c r="F65" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="G64" s="11" t="s">
+      <c r="G65" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H64" s="4" t="s">
+      <c r="H65" s="4" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="65" spans="2:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="5" t="s">
+    <row r="66" spans="2:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B66" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="C65" s="6" t="s">
+      <c r="C66" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="D65" s="6" t="s">
+      <c r="D66" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="E65" s="6" t="s">
+      <c r="E66" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="F65" s="6" t="s">
+      <c r="F66" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="G65" s="14" t="s">
+      <c r="G66" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="H65" s="8" t="s">
+      <c r="H66" s="8" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="66" spans="2:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="15" t="s">
+    <row r="67" spans="2:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="15" t="s">
         <v>290</v>
       </c>
-      <c r="C66" s="16" t="s">
+      <c r="C67" s="16" t="s">
         <v>291</v>
       </c>
-      <c r="D66" s="16" t="s">
+      <c r="D67" s="16" t="s">
         <v>292</v>
       </c>
-      <c r="E66" s="16" t="s">
+      <c r="E67" s="16" t="s">
         <v>293</v>
       </c>
-      <c r="F66" s="16" t="s">
+      <c r="F67" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="G66" s="17" t="s">
+      <c r="G67" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="H66" s="18" t="s">
+      <c r="H67" s="18" t="s">
         <v>294</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" orientation="landscape" r:id="rId1"/>
